--- a/sources/DigComp 3.0 Data Supplement 24 Nov 2025.xlsx
+++ b/sources/DigComp 3.0 Data Supplement 24 Nov 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temp\Python\weblate\digcomp3-l10n\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5C08E5-7B9A-4E40-99C9-A8FD578E5642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF07D1D5-D1CD-4034-B190-069671877C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5400" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5400" windowWidth="51840" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3 Competence Statements'!$A$1:$J$363</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4 Learning Outcomes'!$A$1:$I$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4 Learning Outcomes'!$A$1:$I$523</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7021" uniqueCount="2076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7014" uniqueCount="2075">
   <si>
     <t xml:space="preserve">The full DigComp 3.0 framework is here: https://publications.jrc.ec.europa.eu/repository/handle/JRC144121 </t>
   </si>
@@ -3857,9 +3857,6 @@
     <t xml:space="preserve">Assist others to understand key rights and responsibilities under policies and legislation relating to digital behaviour in a given context. </t>
   </si>
   <si>
-    <t>LO2.5.21</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lead or contribute to digital behaviour policies or initiatives. </t>
   </si>
   <si>
@@ -4013,9 +4010,6 @@
     <t>LO2.6.27</t>
   </si>
   <si>
-    <t xml:space="preserve">Stay informed about developments in digital technologies in relation digital identity management. </t>
-  </si>
-  <si>
     <t>LO2.6.28</t>
   </si>
   <si>
@@ -5027,9 +5021,6 @@
     <t>LO4.3.18</t>
   </si>
   <si>
-    <t xml:space="preserve">Describe strategies to help protect against and respond effectively to harmful behaviour and content. </t>
-  </si>
-  <si>
     <t>LO4.3.19</t>
   </si>
   <si>
@@ -5048,9 +5039,6 @@
     <t>LO4.3.22</t>
   </si>
   <si>
-    <t>Implement strategies to help protect oneself against and respond effectively to harmful behaviour and content.</t>
-  </si>
-  <si>
     <t>LO4.3.23</t>
   </si>
   <si>
@@ -5636,9 +5624,6 @@
     <t>Infrastructure, platforms, or software that are hosted by third-party providers and made available to users through the internet. All infrastructure, platforms, software, or technologies that users access through the internet without requiring additional software downloads can be considered cloud computing services.</t>
   </si>
   <si>
-    <t>In DigComp 3.0, competence statements are short, concrete and technology-neutral descriptions of the kinds of capabilities that individuals at Basic, Intermediate, Advanced and Highly advanced levels could be expected to know or apply, for each of the 21 competences. These are shown in Section 3 of the DigComp 3.0 framework. Competence statements are based on the DigComp 3.0 learning outcomes in Annex 2 of the DigComp 3.0 framework and contain all of the key content in the learning outcomes.</t>
-  </si>
-  <si>
     <t>Complex (task)</t>
   </si>
   <si>
@@ -5876,9 +5861,6 @@
     <t>Digital legislation</t>
   </si>
   <si>
-    <t xml:space="preserve">Since 2018, several pieces of EU digital legislation have been published. Section 1.2 of the DigComp 3.0 framework includes a description of some of the key digital legislation and regulations that could be relevant to consider in the context of DigComp 3.0. </t>
-  </si>
-  <si>
     <t>Digital participation</t>
   </si>
   <si>
@@ -6020,9 +6002,6 @@
     <t>Learning outcomes</t>
   </si>
   <si>
-    <t>Statements of what an individual knows, understands and is able to do on completion of a learning process, which are defined in terms of knowledge, skills and attitudes. DigComp 3.0 includes intended learning outcomes, i.e. what an individual is expected to know, understand or is able to do – rather than achieved learning outcomes – the demonstration of what an individual knows, understands or is able to do. Section 2.5 of the DigComp 3.0 framework provides more detail.</t>
-  </si>
-  <si>
     <t>Licence</t>
   </si>
   <si>
@@ -6297,6 +6276,24 @@
   </si>
   <si>
     <t xml:space="preserve">Respond with effective and respectful communication and behaviour to difficult or complex situations in digital environments. </t>
+  </si>
+  <si>
+    <t>Adjust features of digital environments, and use digital assistance tools and assistive technologies, to suit one’s own and others’ needs and preferences.</t>
+  </si>
+  <si>
+    <t>Describe strategies to help protect against and respond effectively to harmful behaviour, content and deceptive design in digital environments.</t>
+  </si>
+  <si>
+    <t>Implement strategies to help protect oneself against and respond effectively to harmful behaviour, content and deceptive design in digital environments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In DigComp 3.0, competence statements are short, concrete and technology-neutral descriptions of the kinds of capabilities that individuals at Basic, Intermediate, Advanced and Highly advanced levels could be expected to know or apply, for each of the 21 competences. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statements of what an individual knows, understands and is able to do on completion of a learning process, which are defined in terms of knowledge, skills and attitudes. DigComp 3.0 includes intended learning outcomes, i.e. what an individual is expected to know, understand or is able to do – rather than achieved learning outcomes – the demonstration of what an individual knows, understands or is able to do. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since 2018, several pieces of EU digital legislation have been published. The DigComp 3.0 framework includes a description of some of the key digital legislation and regulations that could be relevant to consider in the context of DigComp 3.0. </t>
   </si>
 </sst>
 </file>
@@ -19382,7 +19379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I524"/>
+  <dimension ref="A1:I523"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="18.28515625" customWidth="1"/>
@@ -25295,16 +25292,16 @@
         <v>1244</v>
       </c>
       <c r="F204" s="24" t="s">
-        <v>413</v>
+        <v>2067</v>
       </c>
       <c r="G204" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H204" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I204" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -25323,14 +25320,14 @@
       <c r="E205" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="F205" s="24" t="s">
-        <v>2074</v>
+      <c r="F205" s="26" t="s">
+        <v>421</v>
       </c>
       <c r="G205" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H205" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I205" s="24" t="s">
         <v>213</v>
@@ -25352,17 +25349,17 @@
       <c r="E206" s="25" t="s">
         <v>1246</v>
       </c>
-      <c r="F206" s="26" t="s">
-        <v>421</v>
+      <c r="F206" s="24" t="s">
+        <v>417</v>
       </c>
       <c r="G206" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H206" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I206" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -25382,7 +25379,7 @@
         <v>1247</v>
       </c>
       <c r="F207" s="24" t="s">
-        <v>417</v>
+        <v>1249</v>
       </c>
       <c r="G207" s="24" t="s">
         <v>123</v>
@@ -25411,7 +25408,7 @@
         <v>1248</v>
       </c>
       <c r="F208" s="24" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="G208" s="24" t="s">
         <v>123</v>
@@ -25440,16 +25437,16 @@
         <v>1250</v>
       </c>
       <c r="F209" s="24" t="s">
-        <v>1251</v>
+        <v>2068</v>
       </c>
       <c r="G209" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H209" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I209" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -25469,7 +25466,7 @@
         <v>1252</v>
       </c>
       <c r="F210" s="24" t="s">
-        <v>2075</v>
+        <v>1254</v>
       </c>
       <c r="G210" s="24" t="s">
         <v>123</v>
@@ -25478,7 +25475,7 @@
         <v>879</v>
       </c>
       <c r="I210" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -25498,7 +25495,7 @@
         <v>1253</v>
       </c>
       <c r="F211" s="24" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="G211" s="24" t="s">
         <v>123</v>
@@ -25527,7 +25524,7 @@
         <v>1255</v>
       </c>
       <c r="F212" s="24" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="G212" s="24" t="s">
         <v>123</v>
@@ -25536,7 +25533,7 @@
         <v>879</v>
       </c>
       <c r="I212" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -25556,16 +25553,16 @@
         <v>1257</v>
       </c>
       <c r="F213" s="24" t="s">
-        <v>1258</v>
+        <v>425</v>
       </c>
       <c r="G213" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H213" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I213" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -25585,13 +25582,13 @@
         <v>1259</v>
       </c>
       <c r="F214" s="24" t="s">
-        <v>425</v>
+        <v>1261</v>
       </c>
       <c r="G214" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H214" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I214" s="24" t="s">
         <v>139</v>
@@ -25614,7 +25611,7 @@
         <v>1260</v>
       </c>
       <c r="F215" s="24" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="G215" s="24" t="s">
         <v>129</v>
@@ -25634,25 +25631,25 @@
         <v>63</v>
       </c>
       <c r="C216" s="24">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="D216" s="24" t="s">
-        <v>1232</v>
+        <v>75</v>
       </c>
       <c r="E216" s="25" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F216" s="24" t="s">
-        <v>1263</v>
+        <v>431</v>
       </c>
       <c r="G216" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H216" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I216" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -25672,13 +25669,13 @@
         <v>1264</v>
       </c>
       <c r="F217" s="24" t="s">
-        <v>431</v>
+        <v>1265</v>
       </c>
       <c r="G217" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H217" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I217" s="24" t="s">
         <v>213</v>
@@ -25698,10 +25695,10 @@
         <v>75</v>
       </c>
       <c r="E218" s="25" t="s">
-        <v>1265</v>
-      </c>
-      <c r="F218" s="24" t="s">
         <v>1266</v>
+      </c>
+      <c r="F218" s="15" t="s">
+        <v>1267</v>
       </c>
       <c r="G218" s="24" t="s">
         <v>138</v>
@@ -25727,10 +25724,10 @@
         <v>75</v>
       </c>
       <c r="E219" s="25" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F219" s="15" t="s">
         <v>1268</v>
+      </c>
+      <c r="F219" s="24" t="s">
+        <v>1269</v>
       </c>
       <c r="G219" s="24" t="s">
         <v>138</v>
@@ -25739,7 +25736,7 @@
         <v>872</v>
       </c>
       <c r="I219" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -25756,10 +25753,10 @@
         <v>75</v>
       </c>
       <c r="E220" s="25" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="F220" s="24" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G220" s="24" t="s">
         <v>138</v>
@@ -25785,10 +25782,10 @@
         <v>75</v>
       </c>
       <c r="E221" s="25" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="F221" s="24" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="G221" s="24" t="s">
         <v>138</v>
@@ -25814,10 +25811,10 @@
         <v>75</v>
       </c>
       <c r="E222" s="25" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="F222" s="24" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="G222" s="24" t="s">
         <v>138</v>
@@ -25843,10 +25840,10 @@
         <v>75</v>
       </c>
       <c r="E223" s="25" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F223" s="24" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="G223" s="24" t="s">
         <v>138</v>
@@ -25872,10 +25869,10 @@
         <v>75</v>
       </c>
       <c r="E224" s="25" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="F224" s="24" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="G224" s="24" t="s">
         <v>138</v>
@@ -25884,7 +25881,7 @@
         <v>872</v>
       </c>
       <c r="I224" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -25901,16 +25898,16 @@
         <v>75</v>
       </c>
       <c r="E225" s="25" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="F225" s="24" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="G225" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H225" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I225" s="24" t="s">
         <v>213</v>
@@ -25930,19 +25927,19 @@
         <v>75</v>
       </c>
       <c r="E226" s="25" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F226" s="24" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G226" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H226" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I226" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -25959,16 +25956,16 @@
         <v>75</v>
       </c>
       <c r="E227" s="25" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="F227" s="24" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G227" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H227" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I227" s="24" t="s">
         <v>139</v>
@@ -25988,10 +25985,10 @@
         <v>75</v>
       </c>
       <c r="E228" s="25" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F228" s="24" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G228" s="24" t="s">
         <v>116</v>
@@ -26017,10 +26014,10 @@
         <v>75</v>
       </c>
       <c r="E229" s="25" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F229" s="24" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G229" s="24" t="s">
         <v>116</v>
@@ -26046,10 +26043,10 @@
         <v>75</v>
       </c>
       <c r="E230" s="25" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="F230" s="24" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="G230" s="24" t="s">
         <v>116</v>
@@ -26075,16 +26072,16 @@
         <v>75</v>
       </c>
       <c r="E231" s="25" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="F231" s="24" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G231" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H231" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I231" s="24" t="s">
         <v>139</v>
@@ -26104,10 +26101,10 @@
         <v>75</v>
       </c>
       <c r="E232" s="25" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="F232" s="24" t="s">
-        <v>1294</v>
+        <v>449</v>
       </c>
       <c r="G232" s="24" t="s">
         <v>116</v>
@@ -26136,7 +26133,7 @@
         <v>1295</v>
       </c>
       <c r="F233" s="24" t="s">
-        <v>449</v>
+        <v>1296</v>
       </c>
       <c r="G233" s="24" t="s">
         <v>116</v>
@@ -26162,16 +26159,16 @@
         <v>75</v>
       </c>
       <c r="E234" s="25" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="F234" s="24" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="G234" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H234" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I234" s="24" t="s">
         <v>139</v>
@@ -26191,16 +26188,16 @@
         <v>75</v>
       </c>
       <c r="E235" s="25" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F235" s="24" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="G235" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H235" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I235" s="24" t="s">
         <v>139</v>
@@ -26220,10 +26217,10 @@
         <v>75</v>
       </c>
       <c r="E236" s="25" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F236" s="24" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="G236" s="24" t="s">
         <v>123</v>
@@ -26249,10 +26246,10 @@
         <v>75</v>
       </c>
       <c r="E237" s="25" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="F237" s="24" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="G237" s="24" t="s">
         <v>123</v>
@@ -26261,7 +26258,7 @@
         <v>872</v>
       </c>
       <c r="I237" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
@@ -26278,19 +26275,19 @@
         <v>75</v>
       </c>
       <c r="E238" s="25" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="F238" s="24" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="G238" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H238" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I238" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -26307,10 +26304,10 @@
         <v>75</v>
       </c>
       <c r="E239" s="25" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F239" s="24" t="s">
-        <v>1307</v>
+        <v>457</v>
       </c>
       <c r="G239" s="24" t="s">
         <v>123</v>
@@ -26319,7 +26316,7 @@
         <v>879</v>
       </c>
       <c r="I239" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -26339,7 +26336,7 @@
         <v>1308</v>
       </c>
       <c r="F240" s="24" t="s">
-        <v>457</v>
+        <v>1309</v>
       </c>
       <c r="G240" s="24" t="s">
         <v>123</v>
@@ -26348,7 +26345,7 @@
         <v>879</v>
       </c>
       <c r="I240" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
@@ -26365,10 +26362,10 @@
         <v>75</v>
       </c>
       <c r="E241" s="25" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="F241" s="24" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="G241" s="24" t="s">
         <v>123</v>
@@ -26394,16 +26391,16 @@
         <v>75</v>
       </c>
       <c r="E242" s="25" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="F242" s="24" t="s">
-        <v>1312</v>
+        <v>463</v>
       </c>
       <c r="G242" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H242" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I242" s="24" t="s">
         <v>139</v>
@@ -26426,13 +26423,13 @@
         <v>1313</v>
       </c>
       <c r="F243" s="24" t="s">
-        <v>1314</v>
+        <v>465</v>
       </c>
       <c r="G243" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H243" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I243" s="24" t="s">
         <v>139</v>
@@ -26452,10 +26449,10 @@
         <v>75</v>
       </c>
       <c r="E244" s="25" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F244" s="24" t="s">
         <v>1315</v>
-      </c>
-      <c r="F244" s="24" t="s">
-        <v>465</v>
       </c>
       <c r="G244" s="24" t="s">
         <v>129</v>
@@ -26469,16 +26466,16 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B245" s="24" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C245" s="24">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="D245" s="24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E245" s="25" t="s">
         <v>1316</v>
@@ -26487,10 +26484,10 @@
         <v>1317</v>
       </c>
       <c r="G245" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H245" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I245" s="24" t="s">
         <v>139</v>
@@ -26522,7 +26519,7 @@
         <v>869</v>
       </c>
       <c r="I246" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -26548,7 +26545,7 @@
         <v>138</v>
       </c>
       <c r="H247" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I247" s="24" t="s">
         <v>213</v>
@@ -26580,7 +26577,7 @@
         <v>872</v>
       </c>
       <c r="I248" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -26609,7 +26606,7 @@
         <v>872</v>
       </c>
       <c r="I249" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -26619,11 +26616,11 @@
       <c r="B250" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C250" s="24">
+      <c r="C250" s="25">
         <v>3.1</v>
       </c>
       <c r="D250" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E250" s="25" t="s">
         <v>1326</v>
@@ -26638,7 +26635,7 @@
         <v>872</v>
       </c>
       <c r="I250" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
@@ -26648,11 +26645,11 @@
       <c r="B251" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C251" s="25">
+      <c r="C251" s="24">
         <v>3.1</v>
       </c>
       <c r="D251" s="24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E251" s="25" t="s">
         <v>1328</v>
@@ -26693,10 +26690,10 @@
         <v>138</v>
       </c>
       <c r="H252" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I252" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -26719,10 +26716,10 @@
         <v>1333</v>
       </c>
       <c r="G253" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H253" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I253" s="24" t="s">
         <v>139</v>
@@ -26751,10 +26748,10 @@
         <v>116</v>
       </c>
       <c r="H254" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I254" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
@@ -26783,7 +26780,7 @@
         <v>872</v>
       </c>
       <c r="I255" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -26809,7 +26806,7 @@
         <v>116</v>
       </c>
       <c r="H256" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I256" s="24" t="s">
         <v>139</v>
@@ -26841,7 +26838,7 @@
         <v>879</v>
       </c>
       <c r="I257" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -26870,7 +26867,7 @@
         <v>879</v>
       </c>
       <c r="I258" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -26928,7 +26925,7 @@
         <v>879</v>
       </c>
       <c r="I260" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -26951,13 +26948,13 @@
         <v>1349</v>
       </c>
       <c r="G261" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H261" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I261" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -26977,13 +26974,13 @@
         <v>1350</v>
       </c>
       <c r="F262" s="24" t="s">
-        <v>1351</v>
+        <v>493</v>
       </c>
       <c r="G262" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H262" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I262" s="24" t="s">
         <v>139</v>
@@ -27003,10 +27000,10 @@
         <v>79</v>
       </c>
       <c r="E263" s="25" t="s">
+        <v>1351</v>
+      </c>
+      <c r="F263" s="24" t="s">
         <v>1352</v>
-      </c>
-      <c r="F263" s="24" t="s">
-        <v>493</v>
       </c>
       <c r="G263" s="24" t="s">
         <v>123</v>
@@ -27035,7 +27032,7 @@
         <v>1353</v>
       </c>
       <c r="F264" s="24" t="s">
-        <v>1354</v>
+        <v>497</v>
       </c>
       <c r="G264" s="24" t="s">
         <v>123</v>
@@ -27061,16 +27058,16 @@
         <v>79</v>
       </c>
       <c r="E265" s="25" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F265" s="24" t="s">
         <v>1355</v>
       </c>
-      <c r="F265" s="24" t="s">
-        <v>497</v>
-      </c>
       <c r="G265" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H265" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I265" s="24" t="s">
         <v>139</v>
@@ -27102,7 +27099,7 @@
         <v>869</v>
       </c>
       <c r="I266" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
@@ -27128,10 +27125,10 @@
         <v>129</v>
       </c>
       <c r="H267" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I267" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
@@ -27192,61 +27189,61 @@
         <v>139</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A270" s="24">
+    <row r="270" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="25">
         <v>3</v>
       </c>
-      <c r="B270" s="24" t="s">
+      <c r="B270" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C270" s="24">
-        <v>3.1</v>
-      </c>
-      <c r="D270" s="24" t="s">
-        <v>79</v>
+      <c r="C270" s="25">
+        <v>3.2</v>
+      </c>
+      <c r="D270" s="25" t="s">
+        <v>81</v>
       </c>
       <c r="E270" s="25" t="s">
         <v>1364</v>
       </c>
-      <c r="F270" s="24" t="s">
+      <c r="F270" s="25" t="s">
+        <v>507</v>
+      </c>
+      <c r="G270" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H270" s="25" t="s">
+        <v>869</v>
+      </c>
+      <c r="I270" s="25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="24">
+        <v>3</v>
+      </c>
+      <c r="B271" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C271" s="24">
+        <v>3.2</v>
+      </c>
+      <c r="D271" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E271" s="25" t="s">
         <v>1365</v>
       </c>
-      <c r="G270" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="H270" s="24" t="s">
-        <v>879</v>
-      </c>
-      <c r="I270" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="25">
-        <v>3</v>
-      </c>
-      <c r="B271" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C271" s="25">
-        <v>3.2</v>
-      </c>
-      <c r="D271" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E271" s="25" t="s">
-        <v>1366</v>
-      </c>
-      <c r="F271" s="25" t="s">
-        <v>507</v>
-      </c>
-      <c r="G271" s="25" t="s">
+      <c r="F271" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="G271" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="H271" s="25" t="s">
+      <c r="H271" s="24" t="s">
         <v>869</v>
       </c>
-      <c r="I271" s="25" t="s">
+      <c r="I271" s="24" t="s">
         <v>139</v>
       </c>
     </row>
@@ -27264,16 +27261,16 @@
         <v>81</v>
       </c>
       <c r="E272" s="25" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F272" s="24" t="s">
         <v>1367</v>
-      </c>
-      <c r="F272" s="24" t="s">
-        <v>509</v>
       </c>
       <c r="G272" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H272" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I272" s="24" t="s">
         <v>139</v>
@@ -27305,7 +27302,7 @@
         <v>872</v>
       </c>
       <c r="I273" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -27325,7 +27322,7 @@
         <v>1370</v>
       </c>
       <c r="F274" s="24" t="s">
-        <v>1371</v>
+        <v>511</v>
       </c>
       <c r="G274" s="24" t="s">
         <v>138</v>
@@ -27334,7 +27331,7 @@
         <v>872</v>
       </c>
       <c r="I274" s="24" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
@@ -27351,10 +27348,10 @@
         <v>81</v>
       </c>
       <c r="E275" s="25" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F275" s="24" t="s">
         <v>1372</v>
-      </c>
-      <c r="F275" s="24" t="s">
-        <v>511</v>
       </c>
       <c r="G275" s="24" t="s">
         <v>138</v>
@@ -27363,7 +27360,7 @@
         <v>872</v>
       </c>
       <c r="I275" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -27389,7 +27386,7 @@
         <v>138</v>
       </c>
       <c r="H276" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I276" s="24" t="s">
         <v>139</v>
@@ -27415,10 +27412,10 @@
         <v>1376</v>
       </c>
       <c r="G277" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H277" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I277" s="24" t="s">
         <v>139</v>
@@ -27447,10 +27444,10 @@
         <v>116</v>
       </c>
       <c r="H278" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I278" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
@@ -27508,7 +27505,7 @@
         <v>872</v>
       </c>
       <c r="I280" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
@@ -27534,10 +27531,10 @@
         <v>116</v>
       </c>
       <c r="H281" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I281" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
@@ -27618,10 +27615,10 @@
         <v>1390</v>
       </c>
       <c r="G284" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H284" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I284" s="24" t="s">
         <v>139</v>
@@ -27650,7 +27647,7 @@
         <v>123</v>
       </c>
       <c r="H285" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I285" s="24" t="s">
         <v>139</v>
@@ -27682,7 +27679,7 @@
         <v>872</v>
       </c>
       <c r="I286" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -27708,10 +27705,10 @@
         <v>123</v>
       </c>
       <c r="H287" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I287" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
@@ -27792,10 +27789,10 @@
         <v>1402</v>
       </c>
       <c r="G290" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H290" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I290" s="24" t="s">
         <v>139</v>
@@ -27847,13 +27844,13 @@
         <v>1405</v>
       </c>
       <c r="F292" s="24" t="s">
-        <v>1406</v>
+        <v>531</v>
       </c>
       <c r="G292" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H292" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I292" s="24" t="s">
         <v>139</v>
@@ -27873,10 +27870,10 @@
         <v>81</v>
       </c>
       <c r="E293" s="25" t="s">
+        <v>1406</v>
+      </c>
+      <c r="F293" s="24" t="s">
         <v>1407</v>
-      </c>
-      <c r="F293" s="24" t="s">
-        <v>531</v>
       </c>
       <c r="G293" s="24" t="s">
         <v>129</v>
@@ -27954,10 +27951,10 @@
         <v>77</v>
       </c>
       <c r="C296" s="24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D296" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E296" s="25" t="s">
         <v>1412</v>
@@ -27966,10 +27963,10 @@
         <v>1413</v>
       </c>
       <c r="G296" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H296" s="24" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="I296" s="24" t="s">
         <v>139</v>
@@ -28001,7 +27998,7 @@
         <v>872</v>
       </c>
       <c r="I297" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -28059,7 +28056,7 @@
         <v>872</v>
       </c>
       <c r="I299" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -28117,7 +28114,7 @@
         <v>872</v>
       </c>
       <c r="I301" s="24" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
@@ -28143,10 +28140,10 @@
         <v>138</v>
       </c>
       <c r="H302" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I302" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
@@ -28169,10 +28166,10 @@
         <v>1427</v>
       </c>
       <c r="G303" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H303" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I303" s="24" t="s">
         <v>139</v>
@@ -28230,7 +28227,7 @@
         <v>116</v>
       </c>
       <c r="H305" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I305" s="24" t="s">
         <v>139</v>
@@ -28282,7 +28279,7 @@
         <v>1434</v>
       </c>
       <c r="F307" s="24" t="s">
-        <v>1435</v>
+        <v>549</v>
       </c>
       <c r="G307" s="24" t="s">
         <v>116</v>
@@ -28291,7 +28288,7 @@
         <v>872</v>
       </c>
       <c r="I307" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
@@ -28308,10 +28305,10 @@
         <v>83</v>
       </c>
       <c r="E308" s="25" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F308" s="24" t="s">
         <v>1436</v>
-      </c>
-      <c r="F308" s="24" t="s">
-        <v>549</v>
       </c>
       <c r="G308" s="24" t="s">
         <v>116</v>
@@ -28320,7 +28317,7 @@
         <v>872</v>
       </c>
       <c r="I308" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
@@ -28407,7 +28404,7 @@
         <v>872</v>
       </c>
       <c r="I311" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
@@ -28433,10 +28430,10 @@
         <v>116</v>
       </c>
       <c r="H312" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I312" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
@@ -28459,10 +28456,10 @@
         <v>1446</v>
       </c>
       <c r="G313" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H313" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I313" s="24" t="s">
         <v>139</v>
@@ -28491,7 +28488,7 @@
         <v>123</v>
       </c>
       <c r="H314" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I314" s="24" t="s">
         <v>139</v>
@@ -28542,7 +28539,7 @@
       <c r="E316" s="25" t="s">
         <v>1451</v>
       </c>
-      <c r="F316" s="24" t="s">
+      <c r="F316" s="12" t="s">
         <v>1452</v>
       </c>
       <c r="G316" s="24" t="s">
@@ -28552,7 +28549,7 @@
         <v>872</v>
       </c>
       <c r="I316" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
@@ -28571,17 +28568,17 @@
       <c r="E317" s="25" t="s">
         <v>1453</v>
       </c>
-      <c r="F317" s="12" t="s">
+      <c r="F317" s="24" t="s">
         <v>1454</v>
       </c>
       <c r="G317" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H317" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I317" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
@@ -28601,7 +28598,7 @@
         <v>1455</v>
       </c>
       <c r="F318" s="24" t="s">
-        <v>1456</v>
+        <v>563</v>
       </c>
       <c r="G318" s="24" t="s">
         <v>123</v>
@@ -28627,16 +28624,16 @@
         <v>83</v>
       </c>
       <c r="E319" s="25" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F319" s="24" t="s">
         <v>1457</v>
       </c>
-      <c r="F319" s="24" t="s">
-        <v>563</v>
-      </c>
       <c r="G319" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H319" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I319" s="24" t="s">
         <v>139</v>
@@ -28659,7 +28656,7 @@
         <v>1458</v>
       </c>
       <c r="F320" s="24" t="s">
-        <v>1459</v>
+        <v>565</v>
       </c>
       <c r="G320" s="24" t="s">
         <v>129</v>
@@ -28685,16 +28682,16 @@
         <v>83</v>
       </c>
       <c r="E321" s="25" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F321" s="24" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G321" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H321" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I321" s="24" t="s">
         <v>139</v>
@@ -28714,10 +28711,10 @@
         <v>83</v>
       </c>
       <c r="E322" s="25" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F322" s="24" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G322" s="24" t="s">
         <v>129</v>
@@ -28729,62 +28726,62 @@
         <v>139</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A323" s="24">
+    <row r="323" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="25">
         <v>3</v>
       </c>
-      <c r="B323" s="24" t="s">
+      <c r="B323" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C323" s="24">
-        <v>3.3</v>
-      </c>
-      <c r="D323" s="24" t="s">
-        <v>83</v>
+      <c r="C323" s="25">
+        <v>3.4</v>
+      </c>
+      <c r="D323" s="25" t="s">
+        <v>85</v>
       </c>
       <c r="E323" s="25" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F323" s="25" t="s">
         <v>1462</v>
       </c>
-      <c r="F323" s="24" t="s">
-        <v>569</v>
-      </c>
-      <c r="G323" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="H323" s="24" t="s">
-        <v>879</v>
-      </c>
-      <c r="I323" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="25">
+      <c r="G323" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H323" s="25" t="s">
+        <v>869</v>
+      </c>
+      <c r="I323" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="24">
         <v>3</v>
       </c>
-      <c r="B324" s="25" t="s">
+      <c r="B324" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C324" s="25">
+      <c r="C324" s="24">
         <v>3.4</v>
       </c>
-      <c r="D324" s="25" t="s">
+      <c r="D324" s="24" t="s">
         <v>85</v>
       </c>
       <c r="E324" s="25" t="s">
         <v>1463</v>
       </c>
-      <c r="F324" s="25" t="s">
+      <c r="F324" s="24" t="s">
         <v>1464</v>
       </c>
-      <c r="G324" s="25" t="s">
+      <c r="G324" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="H324" s="25" t="s">
-        <v>869</v>
-      </c>
-      <c r="I324" s="25" t="s">
-        <v>142</v>
+      <c r="H324" s="24" t="s">
+        <v>872</v>
+      </c>
+      <c r="I324" s="24" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
@@ -28813,7 +28810,7 @@
         <v>872</v>
       </c>
       <c r="I325" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
@@ -28842,7 +28839,7 @@
         <v>872</v>
       </c>
       <c r="I326" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
@@ -28926,10 +28923,10 @@
         <v>138</v>
       </c>
       <c r="H329" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I329" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
@@ -28958,7 +28955,7 @@
         <v>879</v>
       </c>
       <c r="I330" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
@@ -28981,13 +28978,13 @@
         <v>1478</v>
       </c>
       <c r="G331" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H331" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I331" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
@@ -29042,7 +29039,7 @@
         <v>116</v>
       </c>
       <c r="H333" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I333" s="24" t="s">
         <v>139</v>
@@ -29074,7 +29071,7 @@
         <v>872</v>
       </c>
       <c r="I334" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
@@ -29248,7 +29245,7 @@
         <v>872</v>
       </c>
       <c r="I340" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
@@ -29267,8 +29264,8 @@
       <c r="E341" s="25" t="s">
         <v>1497</v>
       </c>
-      <c r="F341" s="24" t="s">
-        <v>1498</v>
+      <c r="F341" s="12" t="s">
+        <v>589</v>
       </c>
       <c r="G341" s="24" t="s">
         <v>116</v>
@@ -29294,10 +29291,10 @@
         <v>85</v>
       </c>
       <c r="E342" s="25" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F342" s="24" t="s">
         <v>1499</v>
-      </c>
-      <c r="F342" s="12" t="s">
-        <v>589</v>
       </c>
       <c r="G342" s="24" t="s">
         <v>116</v>
@@ -29361,10 +29358,10 @@
         <v>116</v>
       </c>
       <c r="H344" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I344" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
@@ -29442,16 +29439,16 @@
         <v>1508</v>
       </c>
       <c r="F347" s="24" t="s">
-        <v>1509</v>
+        <v>593</v>
       </c>
       <c r="G347" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H347" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I347" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
@@ -29468,16 +29465,16 @@
         <v>85</v>
       </c>
       <c r="E348" s="25" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F348" s="24" t="s">
         <v>1510</v>
-      </c>
-      <c r="F348" s="24" t="s">
-        <v>593</v>
       </c>
       <c r="G348" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H348" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I348" s="24" t="s">
         <v>142</v>
@@ -29596,7 +29593,7 @@
         <v>872</v>
       </c>
       <c r="I352" s="24" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
@@ -29625,7 +29622,7 @@
         <v>872</v>
       </c>
       <c r="I353" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
@@ -29654,7 +29651,7 @@
         <v>872</v>
       </c>
       <c r="I354" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
@@ -29680,7 +29677,7 @@
         <v>123</v>
       </c>
       <c r="H355" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I355" s="24" t="s">
         <v>142</v>
@@ -29764,10 +29761,10 @@
         <v>1530</v>
       </c>
       <c r="G358" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H358" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I358" s="24" t="s">
         <v>142</v>
@@ -29825,7 +29822,7 @@
         <v>129</v>
       </c>
       <c r="H360" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I360" s="24" t="s">
         <v>142</v>
@@ -29862,31 +29859,31 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B362" s="24" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C362" s="24">
-        <v>3.4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D362" s="24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E362" s="25" t="s">
         <v>1537</v>
       </c>
       <c r="F362" s="24" t="s">
-        <v>1538</v>
+        <v>615</v>
       </c>
       <c r="G362" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H362" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I362" s="24" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
@@ -29903,16 +29900,16 @@
         <v>89</v>
       </c>
       <c r="E363" s="25" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F363" s="24" t="s">
         <v>1539</v>
-      </c>
-      <c r="F363" s="24" t="s">
-        <v>615</v>
       </c>
       <c r="G363" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H363" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I363" s="24" t="s">
         <v>213</v>
@@ -29964,7 +29961,7 @@
         <v>1542</v>
       </c>
       <c r="F365" s="24" t="s">
-        <v>1543</v>
+        <v>619</v>
       </c>
       <c r="G365" s="24" t="s">
         <v>138</v>
@@ -29990,10 +29987,10 @@
         <v>89</v>
       </c>
       <c r="E366" s="25" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F366" s="24" t="s">
         <v>1544</v>
-      </c>
-      <c r="F366" s="24" t="s">
-        <v>619</v>
       </c>
       <c r="G366" s="24" t="s">
         <v>138</v>
@@ -30028,7 +30025,7 @@
         <v>138</v>
       </c>
       <c r="H367" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I367" s="24" t="s">
         <v>213</v>
@@ -30054,13 +30051,13 @@
         <v>1548</v>
       </c>
       <c r="G368" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H368" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I368" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
@@ -30086,7 +30083,7 @@
         <v>116</v>
       </c>
       <c r="H369" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I369" s="24" t="s">
         <v>139</v>
@@ -30118,7 +30115,7 @@
         <v>872</v>
       </c>
       <c r="I370" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
@@ -30144,10 +30141,10 @@
         <v>116</v>
       </c>
       <c r="H371" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I371" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.25">
@@ -30170,13 +30167,13 @@
         <v>1556</v>
       </c>
       <c r="G372" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H372" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I372" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
@@ -30202,10 +30199,10 @@
         <v>123</v>
       </c>
       <c r="H373" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I373" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
@@ -30234,7 +30231,7 @@
         <v>872</v>
       </c>
       <c r="I374" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
@@ -30260,10 +30257,10 @@
         <v>123</v>
       </c>
       <c r="H375" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I375" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
@@ -30292,7 +30289,7 @@
         <v>879</v>
       </c>
       <c r="I376" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.25">
@@ -30312,16 +30309,16 @@
         <v>1565</v>
       </c>
       <c r="F377" s="24" t="s">
-        <v>1566</v>
+        <v>637</v>
       </c>
       <c r="G377" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H377" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I377" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.25">
@@ -30338,16 +30335,16 @@
         <v>89</v>
       </c>
       <c r="E378" s="25" t="s">
+        <v>1566</v>
+      </c>
+      <c r="F378" s="24" t="s">
         <v>1567</v>
-      </c>
-      <c r="F378" s="24" t="s">
-        <v>637</v>
       </c>
       <c r="G378" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H378" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I378" s="24" t="s">
         <v>139</v>
@@ -30419,25 +30416,25 @@
         <v>87</v>
       </c>
       <c r="C381" s="24">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="D381" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E381" s="25" t="s">
         <v>1572</v>
       </c>
       <c r="F381" s="24" t="s">
-        <v>1573</v>
+        <v>646</v>
       </c>
       <c r="G381" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H381" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I381" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
@@ -30454,19 +30451,19 @@
         <v>91</v>
       </c>
       <c r="E382" s="25" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F382" s="24" t="s">
         <v>1574</v>
-      </c>
-      <c r="F382" s="24" t="s">
-        <v>646</v>
       </c>
       <c r="G382" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H382" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I382" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
@@ -30495,7 +30492,7 @@
         <v>872</v>
       </c>
       <c r="I383" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
@@ -30515,7 +30512,7 @@
         <v>1577</v>
       </c>
       <c r="F384" s="24" t="s">
-        <v>1578</v>
+        <v>654</v>
       </c>
       <c r="G384" s="24" t="s">
         <v>138</v>
@@ -30524,7 +30521,7 @@
         <v>872</v>
       </c>
       <c r="I384" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
@@ -30541,10 +30538,10 @@
         <v>91</v>
       </c>
       <c r="E385" s="25" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F385" s="26" t="s">
         <v>1579</v>
-      </c>
-      <c r="F385" s="24" t="s">
-        <v>654</v>
       </c>
       <c r="G385" s="24" t="s">
         <v>138</v>
@@ -30553,7 +30550,7 @@
         <v>872</v>
       </c>
       <c r="I385" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
@@ -30630,14 +30627,14 @@
       <c r="E388" s="25" t="s">
         <v>1584</v>
       </c>
-      <c r="F388" s="26" t="s">
-        <v>1585</v>
+      <c r="F388" s="24" t="s">
+        <v>656</v>
       </c>
       <c r="G388" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H388" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I388" s="24" t="s">
         <v>213</v>
@@ -30657,10 +30654,10 @@
         <v>91</v>
       </c>
       <c r="E389" s="25" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F389" s="24" t="s">
         <v>1586</v>
-      </c>
-      <c r="F389" s="24" t="s">
-        <v>656</v>
       </c>
       <c r="G389" s="24" t="s">
         <v>138</v>
@@ -30688,8 +30685,8 @@
       <c r="E390" s="25" t="s">
         <v>1587</v>
       </c>
-      <c r="F390" s="24" t="s">
-        <v>1588</v>
+      <c r="F390" s="23" t="s">
+        <v>658</v>
       </c>
       <c r="G390" s="24" t="s">
         <v>138</v>
@@ -30715,16 +30712,16 @@
         <v>91</v>
       </c>
       <c r="E391" s="25" t="s">
+        <v>1588</v>
+      </c>
+      <c r="F391" s="24" t="s">
         <v>1589</v>
       </c>
-      <c r="F391" s="23" t="s">
-        <v>658</v>
-      </c>
       <c r="G391" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H391" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I391" s="24" t="s">
         <v>213</v>
@@ -30753,10 +30750,10 @@
         <v>116</v>
       </c>
       <c r="H392" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I392" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
@@ -30785,7 +30782,7 @@
         <v>872</v>
       </c>
       <c r="I393" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
@@ -30833,7 +30830,7 @@
       <c r="E395" s="25" t="s">
         <v>1596</v>
       </c>
-      <c r="F395" s="24" t="s">
+      <c r="F395" s="26" t="s">
         <v>1597</v>
       </c>
       <c r="G395" s="24" t="s">
@@ -30862,8 +30859,8 @@
       <c r="E396" s="25" t="s">
         <v>1598</v>
       </c>
-      <c r="F396" s="26" t="s">
-        <v>1599</v>
+      <c r="F396" s="24" t="s">
+        <v>668</v>
       </c>
       <c r="G396" s="24" t="s">
         <v>116</v>
@@ -30889,10 +30886,10 @@
         <v>91</v>
       </c>
       <c r="E397" s="25" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F397" s="24" t="s">
         <v>1600</v>
-      </c>
-      <c r="F397" s="24" t="s">
-        <v>668</v>
       </c>
       <c r="G397" s="24" t="s">
         <v>116</v>
@@ -30901,7 +30898,7 @@
         <v>872</v>
       </c>
       <c r="I397" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
@@ -30959,7 +30956,7 @@
         <v>872</v>
       </c>
       <c r="I399" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
@@ -30985,7 +30982,7 @@
         <v>116</v>
       </c>
       <c r="H400" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I400" s="24" t="s">
         <v>139</v>
@@ -31008,13 +31005,13 @@
         <v>1607</v>
       </c>
       <c r="F401" s="24" t="s">
-        <v>1608</v>
+        <v>676</v>
       </c>
       <c r="G401" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H401" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I401" s="24" t="s">
         <v>139</v>
@@ -31034,16 +31031,16 @@
         <v>91</v>
       </c>
       <c r="E402" s="25" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="F402" s="24" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G402" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H402" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I402" s="24" t="s">
         <v>139</v>
@@ -31063,10 +31060,10 @@
         <v>91</v>
       </c>
       <c r="E403" s="25" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F403" s="24" t="s">
         <v>1610</v>
-      </c>
-      <c r="F403" s="24" t="s">
-        <v>678</v>
       </c>
       <c r="G403" s="24" t="s">
         <v>123</v>
@@ -31098,10 +31095,10 @@
         <v>1612</v>
       </c>
       <c r="G404" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H404" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I404" s="24" t="s">
         <v>139</v>
@@ -31124,13 +31121,13 @@
         <v>1613</v>
       </c>
       <c r="F405" s="24" t="s">
-        <v>1614</v>
+        <v>684</v>
       </c>
       <c r="G405" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H405" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I405" s="24" t="s">
         <v>139</v>
@@ -31150,10 +31147,10 @@
         <v>91</v>
       </c>
       <c r="E406" s="25" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F406" s="24" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G406" s="24" t="s">
         <v>129</v>
@@ -31165,61 +31162,61 @@
         <v>139</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A407" s="24">
+    <row r="407" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A407" s="25">
         <v>4</v>
       </c>
-      <c r="B407" s="24" t="s">
+      <c r="B407" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C407" s="24">
-        <v>4.2</v>
-      </c>
-      <c r="D407" s="24" t="s">
-        <v>91</v>
+      <c r="C407" s="25">
+        <v>4.3</v>
+      </c>
+      <c r="D407" s="25" t="s">
+        <v>93</v>
       </c>
       <c r="E407" s="25" t="s">
+        <v>1615</v>
+      </c>
+      <c r="F407" s="25" t="s">
         <v>1616</v>
       </c>
-      <c r="F407" s="24" t="s">
-        <v>686</v>
-      </c>
-      <c r="G407" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="H407" s="24" t="s">
-        <v>879</v>
-      </c>
-      <c r="I407" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="408" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="25">
+      <c r="G407" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H407" s="25" t="s">
+        <v>869</v>
+      </c>
+      <c r="I407" s="25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" s="24">
         <v>4</v>
       </c>
-      <c r="B408" s="25" t="s">
+      <c r="B408" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C408" s="25">
+      <c r="C408" s="24">
         <v>4.3</v>
       </c>
-      <c r="D408" s="25" t="s">
+      <c r="D408" s="24" t="s">
         <v>93</v>
       </c>
       <c r="E408" s="25" t="s">
         <v>1617</v>
       </c>
-      <c r="F408" s="25" t="s">
+      <c r="F408" s="24" t="s">
         <v>1618</v>
       </c>
-      <c r="G408" s="25" t="s">
+      <c r="G408" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="H408" s="25" t="s">
+      <c r="H408" s="24" t="s">
         <v>869</v>
       </c>
-      <c r="I408" s="25" t="s">
+      <c r="I408" s="24" t="s">
         <v>213</v>
       </c>
     </row>
@@ -31246,10 +31243,10 @@
         <v>138</v>
       </c>
       <c r="H409" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I409" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
@@ -31365,7 +31362,7 @@
         <v>872</v>
       </c>
       <c r="I413" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
@@ -31394,7 +31391,7 @@
         <v>872</v>
       </c>
       <c r="I414" s="24" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
@@ -31452,7 +31449,7 @@
         <v>872</v>
       </c>
       <c r="I416" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
@@ -31478,10 +31475,10 @@
         <v>138</v>
       </c>
       <c r="H417" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I417" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
@@ -31533,10 +31530,10 @@
         <v>1640</v>
       </c>
       <c r="G419" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H419" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I419" s="24" t="s">
         <v>213</v>
@@ -31594,10 +31591,10 @@
         <v>116</v>
       </c>
       <c r="H421" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I421" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
@@ -31675,7 +31672,7 @@
         <v>1649</v>
       </c>
       <c r="F424" s="24" t="s">
-        <v>1650</v>
+        <v>2070</v>
       </c>
       <c r="G424" s="24" t="s">
         <v>116</v>
@@ -31701,10 +31698,10 @@
         <v>93</v>
       </c>
       <c r="E425" s="25" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="F425" s="24" t="s">
-        <v>1652</v>
+        <v>706</v>
       </c>
       <c r="G425" s="24" t="s">
         <v>116</v>
@@ -31730,10 +31727,10 @@
         <v>93</v>
       </c>
       <c r="E426" s="25" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="F426" s="24" t="s">
-        <v>706</v>
+        <v>1652</v>
       </c>
       <c r="G426" s="24" t="s">
         <v>116</v>
@@ -31759,19 +31756,19 @@
         <v>93</v>
       </c>
       <c r="E427" s="25" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F427" s="24" t="s">
         <v>1654</v>
-      </c>
-      <c r="F427" s="24" t="s">
-        <v>1655</v>
       </c>
       <c r="G427" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H427" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I427" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
@@ -31788,10 +31785,10 @@
         <v>93</v>
       </c>
       <c r="E428" s="25" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="F428" s="24" t="s">
-        <v>1657</v>
+        <v>2071</v>
       </c>
       <c r="G428" s="24" t="s">
         <v>116</v>
@@ -31817,19 +31814,19 @@
         <v>93</v>
       </c>
       <c r="E429" s="25" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="F429" s="24" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="G429" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H429" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I429" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
@@ -31846,10 +31843,10 @@
         <v>93</v>
       </c>
       <c r="E430" s="25" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="F430" s="24" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="G430" s="24" t="s">
         <v>123</v>
@@ -31875,19 +31872,19 @@
         <v>93</v>
       </c>
       <c r="E431" s="25" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="F431" s="24" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="G431" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H431" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I431" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
@@ -31904,10 +31901,10 @@
         <v>93</v>
       </c>
       <c r="E432" s="25" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="F432" s="24" t="s">
-        <v>1665</v>
+        <v>716</v>
       </c>
       <c r="G432" s="24" t="s">
         <v>123</v>
@@ -31916,7 +31913,7 @@
         <v>879</v>
       </c>
       <c r="I432" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
@@ -31933,10 +31930,10 @@
         <v>93</v>
       </c>
       <c r="E433" s="25" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
       <c r="F433" s="24" t="s">
-        <v>716</v>
+        <v>1664</v>
       </c>
       <c r="G433" s="24" t="s">
         <v>123</v>
@@ -31962,10 +31959,10 @@
         <v>93</v>
       </c>
       <c r="E434" s="25" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="F434" s="24" t="s">
-        <v>1668</v>
+        <v>722</v>
       </c>
       <c r="G434" s="24" t="s">
         <v>123</v>
@@ -31991,10 +31988,10 @@
         <v>93</v>
       </c>
       <c r="E435" s="25" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
       <c r="F435" s="24" t="s">
-        <v>722</v>
+        <v>1667</v>
       </c>
       <c r="G435" s="24" t="s">
         <v>123</v>
@@ -32020,16 +32017,16 @@
         <v>93</v>
       </c>
       <c r="E436" s="25" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="F436" s="24" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="G436" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H436" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I436" s="24" t="s">
         <v>139</v>
@@ -32049,16 +32046,16 @@
         <v>93</v>
       </c>
       <c r="E437" s="25" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="F437" s="24" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="G437" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H437" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I437" s="24" t="s">
         <v>139</v>
@@ -32078,10 +32075,10 @@
         <v>93</v>
       </c>
       <c r="E438" s="25" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="F438" s="24" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="G438" s="24" t="s">
         <v>129</v>
@@ -32107,10 +32104,10 @@
         <v>93</v>
       </c>
       <c r="E439" s="25" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="F439" s="24" t="s">
-        <v>1677</v>
+        <v>730</v>
       </c>
       <c r="G439" s="24" t="s">
         <v>129</v>
@@ -32130,25 +32127,25 @@
         <v>87</v>
       </c>
       <c r="C440" s="24">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D440" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E440" s="25" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
       <c r="F440" s="24" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G440" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H440" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I440" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
@@ -32165,19 +32162,19 @@
         <v>95</v>
       </c>
       <c r="E441" s="25" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
       <c r="F441" s="24" t="s">
-        <v>732</v>
+        <v>1677</v>
       </c>
       <c r="G441" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H441" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I441" s="24" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.25">
@@ -32194,10 +32191,10 @@
         <v>95</v>
       </c>
       <c r="E442" s="25" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="F442" s="24" t="s">
-        <v>1681</v>
+        <v>736</v>
       </c>
       <c r="G442" s="24" t="s">
         <v>138</v>
@@ -32206,7 +32203,7 @@
         <v>872</v>
       </c>
       <c r="I442" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.25">
@@ -32223,10 +32220,10 @@
         <v>95</v>
       </c>
       <c r="E443" s="25" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
       <c r="F443" s="24" t="s">
-        <v>736</v>
+        <v>1680</v>
       </c>
       <c r="G443" s="24" t="s">
         <v>138</v>
@@ -32252,10 +32249,10 @@
         <v>95</v>
       </c>
       <c r="E444" s="25" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="F444" s="24" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="G444" s="24" t="s">
         <v>138</v>
@@ -32281,16 +32278,16 @@
         <v>95</v>
       </c>
       <c r="E445" s="25" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="F445" s="24" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="G445" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H445" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I445" s="24" t="s">
         <v>139</v>
@@ -32310,16 +32307,16 @@
         <v>95</v>
       </c>
       <c r="E446" s="25" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="F446" s="24" t="s">
-        <v>1688</v>
+        <v>742</v>
       </c>
       <c r="G446" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H446" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I446" s="24" t="s">
         <v>139</v>
@@ -32339,16 +32336,16 @@
         <v>95</v>
       </c>
       <c r="E447" s="25" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="F447" s="24" t="s">
-        <v>742</v>
+        <v>1687</v>
       </c>
       <c r="G447" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H447" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I447" s="24" t="s">
         <v>139</v>
@@ -32368,10 +32365,10 @@
         <v>95</v>
       </c>
       <c r="E448" s="25" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="F448" s="24" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="G448" s="24" t="s">
         <v>116</v>
@@ -32397,10 +32394,10 @@
         <v>95</v>
       </c>
       <c r="E449" s="25" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="F449" s="24" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="G449" s="24" t="s">
         <v>116</v>
@@ -32426,10 +32423,10 @@
         <v>95</v>
       </c>
       <c r="E450" s="25" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="F450" s="24" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="G450" s="24" t="s">
         <v>116</v>
@@ -32438,7 +32435,7 @@
         <v>872</v>
       </c>
       <c r="I450" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.25">
@@ -32455,19 +32452,19 @@
         <v>95</v>
       </c>
       <c r="E451" s="25" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="F451" s="24" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="G451" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H451" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I451" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.25">
@@ -32484,16 +32481,16 @@
         <v>95</v>
       </c>
       <c r="E452" s="25" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="F452" s="24" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="G452" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H452" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I452" s="24" t="s">
         <v>139</v>
@@ -32513,16 +32510,16 @@
         <v>95</v>
       </c>
       <c r="E453" s="25" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="F453" s="24" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="G453" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H453" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I453" s="24" t="s">
         <v>139</v>
@@ -32542,10 +32539,10 @@
         <v>95</v>
       </c>
       <c r="E454" s="25" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="F454" s="24" t="s">
-        <v>1703</v>
+        <v>756</v>
       </c>
       <c r="G454" s="24" t="s">
         <v>123</v>
@@ -32571,16 +32568,16 @@
         <v>95</v>
       </c>
       <c r="E455" s="25" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
       <c r="F455" s="24" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="G455" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H455" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I455" s="24" t="s">
         <v>139</v>
@@ -32600,10 +32597,10 @@
         <v>95</v>
       </c>
       <c r="E456" s="25" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="F456" s="24" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G456" s="24" t="s">
         <v>129</v>
@@ -32629,16 +32626,16 @@
         <v>95</v>
       </c>
       <c r="E457" s="25" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
       <c r="F457" s="24" t="s">
-        <v>760</v>
+        <v>1704</v>
       </c>
       <c r="G457" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H457" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I457" s="24" t="s">
         <v>139</v>
@@ -32658,10 +32655,10 @@
         <v>95</v>
       </c>
       <c r="E458" s="25" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="F458" s="24" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="G458" s="24" t="s">
         <v>129</v>
@@ -32675,31 +32672,31 @@
     </row>
     <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B459" s="24" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C459" s="24">
-        <v>4.4000000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D459" s="24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E459" s="25" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="F459" s="24" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="G459" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H459" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I459" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.25">
@@ -32716,10 +32713,10 @@
         <v>99</v>
       </c>
       <c r="E460" s="25" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="F460" s="24" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="G460" s="24" t="s">
         <v>138</v>
@@ -32745,16 +32742,16 @@
         <v>99</v>
       </c>
       <c r="E461" s="25" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="F461" s="24" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="G461" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H461" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I461" s="24" t="s">
         <v>213</v>
@@ -32774,10 +32771,10 @@
         <v>99</v>
       </c>
       <c r="E462" s="25" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="F462" s="24" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="G462" s="24" t="s">
         <v>138</v>
@@ -32803,10 +32800,10 @@
         <v>99</v>
       </c>
       <c r="E463" s="25" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="F463" s="24" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="G463" s="24" t="s">
         <v>138</v>
@@ -32832,16 +32829,16 @@
         <v>99</v>
       </c>
       <c r="E464" s="25" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="F464" s="24" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="G464" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H464" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I464" s="24" t="s">
         <v>213</v>
@@ -32861,10 +32858,10 @@
         <v>99</v>
       </c>
       <c r="E465" s="25" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="F465" s="24" t="s">
-        <v>1722</v>
+        <v>773</v>
       </c>
       <c r="G465" s="24" t="s">
         <v>138</v>
@@ -32890,16 +32887,16 @@
         <v>99</v>
       </c>
       <c r="E466" s="25" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
       <c r="F466" s="24" t="s">
-        <v>773</v>
+        <v>1721</v>
       </c>
       <c r="G466" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H466" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I466" s="24" t="s">
         <v>213</v>
@@ -32919,19 +32916,19 @@
         <v>99</v>
       </c>
       <c r="E467" s="25" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="F467" s="24" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="G467" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H467" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I467" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.25">
@@ -32948,10 +32945,10 @@
         <v>99</v>
       </c>
       <c r="E468" s="25" t="s">
-        <v>1726</v>
-      </c>
-      <c r="F468" s="24" t="s">
-        <v>1727</v>
+        <v>1724</v>
+      </c>
+      <c r="F468" s="15" t="s">
+        <v>779</v>
       </c>
       <c r="G468" s="24" t="s">
         <v>116</v>
@@ -32960,7 +32957,7 @@
         <v>879</v>
       </c>
       <c r="I468" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.25">
@@ -32977,16 +32974,16 @@
         <v>99</v>
       </c>
       <c r="E469" s="25" t="s">
-        <v>1728</v>
-      </c>
-      <c r="F469" s="15" t="s">
-        <v>779</v>
+        <v>1725</v>
+      </c>
+      <c r="F469" s="24" t="s">
+        <v>1726</v>
       </c>
       <c r="G469" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H469" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I469" s="24" t="s">
         <v>213</v>
@@ -33006,16 +33003,16 @@
         <v>99</v>
       </c>
       <c r="E470" s="25" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="F470" s="24" t="s">
-        <v>1730</v>
+        <v>783</v>
       </c>
       <c r="G470" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H470" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I470" s="24" t="s">
         <v>213</v>
@@ -33035,10 +33032,10 @@
         <v>99</v>
       </c>
       <c r="E471" s="25" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
       <c r="F471" s="24" t="s">
-        <v>783</v>
+        <v>1729</v>
       </c>
       <c r="G471" s="24" t="s">
         <v>123</v>
@@ -33047,7 +33044,7 @@
         <v>879</v>
       </c>
       <c r="I471" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.25">
@@ -33064,19 +33061,19 @@
         <v>99</v>
       </c>
       <c r="E472" s="25" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="F472" s="24" t="s">
-        <v>1733</v>
+        <v>787</v>
       </c>
       <c r="G472" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H472" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I472" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.25">
@@ -33093,19 +33090,19 @@
         <v>99</v>
       </c>
       <c r="E473" s="25" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
       <c r="F473" s="24" t="s">
-        <v>787</v>
+        <v>1732</v>
       </c>
       <c r="G473" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H473" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I473" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.25">
@@ -33116,25 +33113,25 @@
         <v>97</v>
       </c>
       <c r="C474" s="24">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="D474" s="24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E474" s="25" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="F474" s="24" t="s">
-        <v>1736</v>
+        <v>792</v>
       </c>
       <c r="G474" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H474" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I474" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.25">
@@ -33151,16 +33148,16 @@
         <v>101</v>
       </c>
       <c r="E475" s="25" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="F475" s="24" t="s">
-        <v>792</v>
+        <v>1735</v>
       </c>
       <c r="G475" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H475" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I475" s="24" t="s">
         <v>213</v>
@@ -33180,10 +33177,10 @@
         <v>101</v>
       </c>
       <c r="E476" s="25" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="F476" s="24" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="G476" s="24" t="s">
         <v>138</v>
@@ -33192,7 +33189,7 @@
         <v>872</v>
       </c>
       <c r="I476" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.25">
@@ -33209,10 +33206,10 @@
         <v>101</v>
       </c>
       <c r="E477" s="25" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="F477" s="24" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="G477" s="24" t="s">
         <v>138</v>
@@ -33221,7 +33218,7 @@
         <v>872</v>
       </c>
       <c r="I477" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.25">
@@ -33238,10 +33235,10 @@
         <v>101</v>
       </c>
       <c r="E478" s="25" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="F478" s="24" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="G478" s="24" t="s">
         <v>138</v>
@@ -33250,7 +33247,7 @@
         <v>872</v>
       </c>
       <c r="I478" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.25">
@@ -33267,16 +33264,16 @@
         <v>101</v>
       </c>
       <c r="E479" s="25" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="F479" s="24" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="G479" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H479" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I479" s="24" t="s">
         <v>139</v>
@@ -33296,10 +33293,10 @@
         <v>101</v>
       </c>
       <c r="E480" s="25" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="F480" s="24" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="G480" s="24" t="s">
         <v>138</v>
@@ -33325,16 +33322,16 @@
         <v>101</v>
       </c>
       <c r="E481" s="25" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="F481" s="24" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="G481" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H481" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I481" s="24" t="s">
         <v>139</v>
@@ -33354,16 +33351,16 @@
         <v>101</v>
       </c>
       <c r="E482" s="25" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="F482" s="24" t="s">
-        <v>1751</v>
+        <v>802</v>
       </c>
       <c r="G482" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H482" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I482" s="24" t="s">
         <v>139</v>
@@ -33383,10 +33380,10 @@
         <v>101</v>
       </c>
       <c r="E483" s="25" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
       <c r="F483" s="24" t="s">
-        <v>802</v>
+        <v>1750</v>
       </c>
       <c r="G483" s="24" t="s">
         <v>116</v>
@@ -33412,16 +33409,16 @@
         <v>101</v>
       </c>
       <c r="E484" s="25" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="F484" s="24" t="s">
-        <v>1754</v>
+        <v>804</v>
       </c>
       <c r="G484" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H484" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I484" s="24" t="s">
         <v>139</v>
@@ -33441,16 +33438,16 @@
         <v>101</v>
       </c>
       <c r="E485" s="25" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
       <c r="F485" s="24" t="s">
-        <v>804</v>
+        <v>2069</v>
       </c>
       <c r="G485" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H485" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I485" s="24" t="s">
         <v>139</v>
@@ -33470,10 +33467,10 @@
         <v>101</v>
       </c>
       <c r="E486" s="25" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
       <c r="F486" s="24" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="G486" s="24" t="s">
         <v>123</v>
@@ -33499,10 +33496,10 @@
         <v>101</v>
       </c>
       <c r="E487" s="25" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
       <c r="F487" s="24" t="s">
-        <v>808</v>
+        <v>1755</v>
       </c>
       <c r="G487" s="24" t="s">
         <v>123</v>
@@ -33528,16 +33525,16 @@
         <v>101</v>
       </c>
       <c r="E488" s="25" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="F488" s="24" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="G488" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H488" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I488" s="24" t="s">
         <v>139</v>
@@ -33557,16 +33554,16 @@
         <v>101</v>
       </c>
       <c r="E489" s="25" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="F489" s="24" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="G489" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H489" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I489" s="24" t="s">
         <v>139</v>
@@ -33586,10 +33583,10 @@
         <v>101</v>
       </c>
       <c r="E490" s="25" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="F490" s="24" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="G490" s="24" t="s">
         <v>129</v>
@@ -33609,22 +33606,22 @@
         <v>97</v>
       </c>
       <c r="C491" s="24">
-        <v>5.2</v>
-      </c>
-      <c r="D491" s="24" t="s">
-        <v>101</v>
+        <v>5.3</v>
+      </c>
+      <c r="D491" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="E491" s="25" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F491" s="24" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="G491" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H491" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I491" s="24" t="s">
         <v>139</v>
@@ -33644,16 +33641,16 @@
         <v>103</v>
       </c>
       <c r="E492" s="25" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="F492" s="24" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="G492" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H492" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I492" s="24" t="s">
         <v>139</v>
@@ -33673,10 +33670,10 @@
         <v>103</v>
       </c>
       <c r="E493" s="25" t="s">
-        <v>1768</v>
-      </c>
-      <c r="F493" s="24" t="s">
-        <v>1769</v>
+        <v>1766</v>
+      </c>
+      <c r="F493" s="12" t="s">
+        <v>822</v>
       </c>
       <c r="G493" s="24" t="s">
         <v>138</v>
@@ -33702,16 +33699,16 @@
         <v>103</v>
       </c>
       <c r="E494" s="25" t="s">
-        <v>1770</v>
-      </c>
-      <c r="F494" s="12" t="s">
-        <v>822</v>
+        <v>1767</v>
+      </c>
+      <c r="F494" s="24" t="s">
+        <v>1768</v>
       </c>
       <c r="G494" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H494" s="24" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="I494" s="24" t="s">
         <v>139</v>
@@ -33731,16 +33728,16 @@
         <v>103</v>
       </c>
       <c r="E495" s="25" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="F495" s="24" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="G495" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H495" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I495" s="24" t="s">
         <v>139</v>
@@ -33760,10 +33757,10 @@
         <v>103</v>
       </c>
       <c r="E496" s="25" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="F496" s="24" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="G496" s="24" t="s">
         <v>116</v>
@@ -33789,10 +33786,10 @@
         <v>103</v>
       </c>
       <c r="E497" s="25" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="F497" s="24" t="s">
-        <v>1776</v>
+        <v>826</v>
       </c>
       <c r="G497" s="24" t="s">
         <v>116</v>
@@ -33801,7 +33798,7 @@
         <v>872</v>
       </c>
       <c r="I497" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.25">
@@ -33818,19 +33815,19 @@
         <v>103</v>
       </c>
       <c r="E498" s="25" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="F498" s="24" t="s">
-        <v>826</v>
+        <v>1775</v>
       </c>
       <c r="G498" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H498" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I498" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.25">
@@ -33847,10 +33844,10 @@
         <v>103</v>
       </c>
       <c r="E499" s="25" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="F499" s="24" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="G499" s="24" t="s">
         <v>116</v>
@@ -33876,16 +33873,16 @@
         <v>103</v>
       </c>
       <c r="E500" s="25" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="F500" s="24" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="G500" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H500" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I500" s="24" t="s">
         <v>139</v>
@@ -33905,16 +33902,16 @@
         <v>103</v>
       </c>
       <c r="E501" s="25" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="F501" s="24" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="G501" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H501" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I501" s="24" t="s">
         <v>139</v>
@@ -33934,10 +33931,10 @@
         <v>103</v>
       </c>
       <c r="E502" s="25" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="F502" s="24" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="G502" s="24" t="s">
         <v>123</v>
@@ -33963,10 +33960,10 @@
         <v>103</v>
       </c>
       <c r="E503" s="25" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="F503" s="24" t="s">
-        <v>1787</v>
+        <v>832</v>
       </c>
       <c r="G503" s="24" t="s">
         <v>123</v>
@@ -33992,13 +33989,13 @@
         <v>103</v>
       </c>
       <c r="E504" s="25" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="F504" s="24" t="s">
-        <v>832</v>
+        <v>1786</v>
       </c>
       <c r="G504" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H504" s="24" t="s">
         <v>879</v>
@@ -34021,10 +34018,10 @@
         <v>103</v>
       </c>
       <c r="E505" s="25" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="F505" s="24" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="G505" s="24" t="s">
         <v>129</v>
@@ -34050,10 +34047,10 @@
         <v>103</v>
       </c>
       <c r="E506" s="25" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="F506" s="24" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="G506" s="24" t="s">
         <v>129</v>
@@ -34073,22 +34070,22 @@
         <v>97</v>
       </c>
       <c r="C507" s="24">
-        <v>5.3</v>
-      </c>
-      <c r="D507" s="2" t="s">
-        <v>103</v>
+        <v>5.4</v>
+      </c>
+      <c r="D507" s="24" t="s">
+        <v>105</v>
       </c>
       <c r="E507" s="25" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="F507" s="24" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="G507" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H507" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I507" s="24" t="s">
         <v>139</v>
@@ -34108,10 +34105,10 @@
         <v>105</v>
       </c>
       <c r="E508" s="25" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="F508" s="24" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="G508" s="24" t="s">
         <v>138</v>
@@ -34120,7 +34117,7 @@
         <v>869</v>
       </c>
       <c r="I508" s="24" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
@@ -34137,19 +34134,19 @@
         <v>105</v>
       </c>
       <c r="E509" s="25" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="F509" s="24" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="G509" s="24" t="s">
         <v>138</v>
       </c>
       <c r="H509" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I509" s="24" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.25">
@@ -34166,10 +34163,10 @@
         <v>105</v>
       </c>
       <c r="E510" s="25" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="F510" s="24" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="G510" s="24" t="s">
         <v>138</v>
@@ -34195,10 +34192,10 @@
         <v>105</v>
       </c>
       <c r="E511" s="25" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="F511" s="24" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="G511" s="24" t="s">
         <v>138</v>
@@ -34224,16 +34221,16 @@
         <v>105</v>
       </c>
       <c r="E512" s="25" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="F512" s="24" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="G512" s="24" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H512" s="24" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="I512" s="24" t="s">
         <v>139</v>
@@ -34253,10 +34250,10 @@
         <v>105</v>
       </c>
       <c r="E513" s="25" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="F513" s="24" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="G513" s="24" t="s">
         <v>116</v>
@@ -34282,16 +34279,16 @@
         <v>105</v>
       </c>
       <c r="E514" s="25" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="F514" s="24" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="G514" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H514" s="24" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I514" s="24" t="s">
         <v>139</v>
@@ -34311,16 +34308,16 @@
         <v>105</v>
       </c>
       <c r="E515" s="25" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="F515" s="24" t="s">
-        <v>1810</v>
+        <v>850</v>
       </c>
       <c r="G515" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H515" s="24" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="I515" s="24" t="s">
         <v>139</v>
@@ -34340,16 +34337,16 @@
         <v>105</v>
       </c>
       <c r="E516" s="25" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="F516" s="24" t="s">
-        <v>850</v>
+        <v>1809</v>
       </c>
       <c r="G516" s="24" t="s">
         <v>116</v>
       </c>
       <c r="H516" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I516" s="24" t="s">
         <v>139</v>
@@ -34369,13 +34366,13 @@
         <v>105</v>
       </c>
       <c r="E517" s="25" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="F517" s="24" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="G517" s="24" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="H517" s="24" t="s">
         <v>869</v>
@@ -34398,10 +34395,10 @@
         <v>105</v>
       </c>
       <c r="E518" s="25" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="F518" s="24" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="G518" s="24" t="s">
         <v>123</v>
@@ -34427,16 +34424,16 @@
         <v>105</v>
       </c>
       <c r="E519" s="25" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="F519" s="24" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="G519" s="24" t="s">
         <v>123</v>
       </c>
       <c r="H519" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I519" s="24" t="s">
         <v>139</v>
@@ -34456,10 +34453,10 @@
         <v>105</v>
       </c>
       <c r="E520" s="25" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="F520" s="24" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="G520" s="24" t="s">
         <v>123</v>
@@ -34485,16 +34482,16 @@
         <v>105</v>
       </c>
       <c r="E521" s="25" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="F521" s="24" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="G521" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H521" s="24" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="I521" s="24" t="s">
         <v>139</v>
@@ -34514,16 +34511,16 @@
         <v>105</v>
       </c>
       <c r="E522" s="25" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="F522" s="24" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="G522" s="24" t="s">
         <v>129</v>
       </c>
       <c r="H522" s="24" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="I522" s="24" t="s">
         <v>139</v>
@@ -34543,10 +34540,10 @@
         <v>105</v>
       </c>
       <c r="E523" s="25" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="F523" s="24" t="s">
-        <v>1825</v>
+        <v>866</v>
       </c>
       <c r="G523" s="24" t="s">
         <v>129</v>
@@ -34558,37 +34555,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A524" s="24">
-        <v>5</v>
-      </c>
-      <c r="B524" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C524" s="24">
-        <v>5.4</v>
-      </c>
-      <c r="D524" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E524" s="25" t="s">
-        <v>1826</v>
-      </c>
-      <c r="F524" s="24" t="s">
-        <v>866</v>
-      </c>
-      <c r="G524" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="H524" s="24" t="s">
-        <v>879</v>
-      </c>
-      <c r="I524" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I524" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
+  <autoFilter ref="A1:I523" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -34614,826 +34582,826 @@
     </row>
     <row r="2" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>1827</v>
+        <v>1823</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>1832</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>1834</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>1840</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>1850</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>1851</v>
+        <v>1847</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>1852</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>1853</v>
+        <v>1849</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>1854</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>135</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>1855</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>1858</v>
+        <v>1853</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>1859</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="102" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>1861</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>1862</v>
+        <v>1857</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>1863</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>1867</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>1872</v>
+        <v>1867</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>1874</v>
+        <v>1869</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>1875</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>1878</v>
+        <v>1873</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>1881</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="B31" s="29" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="B37" s="29" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="102" x14ac:dyDescent="0.25">
       <c r="A42" s="31" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="28" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
-        <v>1912</v>
+        <v>1907</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A47" s="31" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A53" s="32" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A54" s="28" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>1935</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
-        <v>1936</v>
+        <v>1930</v>
       </c>
       <c r="B57" s="29" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
-        <v>1938</v>
+        <v>1932</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>1939</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A59" s="28" t="s">
-        <v>1940</v>
+        <v>1934</v>
       </c>
       <c r="B59" s="29" t="s">
-        <v>1941</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
-        <v>1942</v>
+        <v>1936</v>
       </c>
       <c r="B60" s="29" t="s">
-        <v>1943</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="28" t="s">
-        <v>1944</v>
+        <v>1938</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>1945</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
-        <v>1946</v>
+        <v>1940</v>
       </c>
       <c r="B62" s="29" t="s">
-        <v>1947</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="28" t="s">
-        <v>1948</v>
+        <v>1942</v>
       </c>
       <c r="B63" s="29" t="s">
-        <v>1949</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
-        <v>1950</v>
+        <v>1944</v>
       </c>
       <c r="B64" s="29" t="s">
-        <v>1951</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
-        <v>1952</v>
+        <v>1946</v>
       </c>
       <c r="B65" s="29" t="s">
-        <v>1953</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
-        <v>1954</v>
+        <v>1948</v>
       </c>
       <c r="B66" s="29" t="s">
-        <v>1955</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
-        <v>1956</v>
+        <v>1950</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>1957</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
-        <v>1958</v>
+        <v>1952</v>
       </c>
       <c r="B68" s="29" t="s">
-        <v>1959</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A69" s="32" t="s">
-        <v>1960</v>
+        <v>1954</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>1961</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
-        <v>1962</v>
+        <v>1956</v>
       </c>
       <c r="B70" s="29" t="s">
-        <v>1963</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A71" s="28" t="s">
-        <v>1964</v>
+        <v>1958</v>
       </c>
       <c r="B71" s="29" t="s">
-        <v>1965</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
-        <v>1966</v>
+        <v>1960</v>
       </c>
       <c r="B72" s="29" t="s">
-        <v>1967</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="B73" s="29" t="s">
-        <v>1969</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
-        <v>1970</v>
+        <v>1964</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>1971</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
-        <v>1972</v>
+        <v>1966</v>
       </c>
       <c r="B75" s="29" t="s">
-        <v>1973</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="102" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
-        <v>1974</v>
+        <v>1968</v>
       </c>
       <c r="B76" s="29" t="s">
-        <v>1975</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A77" s="28" t="s">
-        <v>1976</v>
+        <v>1970</v>
       </c>
       <c r="B77" s="29" t="s">
-        <v>1977</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
-        <v>1978</v>
+        <v>1972</v>
       </c>
       <c r="B78" s="29" t="s">
-        <v>1979</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="31" t="s">
-        <v>1980</v>
+        <v>1974</v>
       </c>
       <c r="B79" s="29" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A80" s="31" t="s">
-        <v>1982</v>
+        <v>1976</v>
       </c>
       <c r="B80" s="29" t="s">
-        <v>1983</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="102" x14ac:dyDescent="0.25">
       <c r="A81" s="31" t="s">
-        <v>1984</v>
+        <v>1977</v>
       </c>
       <c r="B81" s="29" t="s">
-        <v>1985</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
-        <v>1986</v>
+        <v>1979</v>
       </c>
       <c r="B82" s="29" t="s">
-        <v>1987</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A83" s="28" t="s">
-        <v>1988</v>
+        <v>1981</v>
       </c>
       <c r="B83" s="29" t="s">
-        <v>1989</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
-        <v>1990</v>
+        <v>1983</v>
       </c>
       <c r="B84" s="29" t="s">
-        <v>1991</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="28" t="s">
-        <v>1992</v>
+        <v>1985</v>
       </c>
       <c r="B85" s="29" t="s">
-        <v>1993</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="102" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
-        <v>1994</v>
+        <v>1987</v>
       </c>
       <c r="B86" s="29" t="s">
-        <v>1995</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A87" s="32" t="s">
-        <v>1996</v>
+        <v>1989</v>
       </c>
       <c r="B87" s="29" t="s">
-        <v>1997</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
-        <v>1998</v>
+        <v>1991</v>
       </c>
       <c r="B88" s="29" t="s">
-        <v>1999</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="28" t="s">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>1945</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
-        <v>2001</v>
+        <v>1994</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>1945</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A91" s="28" t="s">
-        <v>2002</v>
+        <v>1995</v>
       </c>
       <c r="B91" s="29" t="s">
-        <v>2003</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
-        <v>2004</v>
+        <v>1997</v>
       </c>
       <c r="B92" s="29" t="s">
-        <v>2005</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A93" s="28" t="s">
-        <v>2006</v>
+        <v>1999</v>
       </c>
       <c r="B93" s="29" t="s">
-        <v>2007</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A94" s="28" t="s">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="B94" s="29" t="s">
-        <v>2009</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A95" s="28" t="s">
-        <v>2010</v>
+        <v>2003</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>2011</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A96" s="28" t="s">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="B96" s="29" t="s">
-        <v>2013</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="28" t="s">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="B97" s="28" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="B98" s="29" t="s">
-        <v>2016</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A99" s="28" t="s">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B99" s="29" t="s">
-        <v>2018</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A100" s="28" t="s">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="B100" s="29" t="s">
-        <v>2020</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A101" s="28" t="s">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B101" s="29" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="B102" s="30" t="s">
-        <v>2024</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A103" s="28" t="s">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="B103" s="29" t="s">
-        <v>2026</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
-        <v>2027</v>
+        <v>2020</v>
       </c>
       <c r="B104" s="29" t="s">
-        <v>2028</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
@@ -35441,183 +35409,183 @@
         <v>867</v>
       </c>
       <c r="B105" s="29" t="s">
-        <v>2029</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
-        <v>2030</v>
+        <v>2023</v>
       </c>
       <c r="B106" s="29" t="s">
-        <v>2031</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A107" s="28" t="s">
-        <v>2032</v>
+        <v>2025</v>
       </c>
       <c r="B107" s="29" t="s">
-        <v>2033</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
-        <v>2034</v>
+        <v>2027</v>
       </c>
       <c r="B108" s="29" t="s">
-        <v>2035</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A109" s="28" t="s">
-        <v>2036</v>
+        <v>2029</v>
       </c>
       <c r="B109" s="29" t="s">
-        <v>2037</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
-        <v>2038</v>
+        <v>2031</v>
       </c>
       <c r="B110" s="29" t="s">
-        <v>2039</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A111" s="28" t="s">
-        <v>2040</v>
+        <v>2033</v>
       </c>
       <c r="B111" s="29" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
-        <v>2042</v>
+        <v>2035</v>
       </c>
       <c r="B112" s="29" t="s">
-        <v>2043</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A113" s="28" t="s">
-        <v>2044</v>
+        <v>2037</v>
       </c>
       <c r="B113" s="29" t="s">
-        <v>2045</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
-        <v>2046</v>
+        <v>2039</v>
       </c>
       <c r="B114" s="29" t="s">
-        <v>2047</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A115" s="28" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
       <c r="B115" s="29" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
       <c r="B116" s="29" t="s">
-        <v>2051</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A117" s="28" t="s">
-        <v>2052</v>
+        <v>2045</v>
       </c>
       <c r="B117" s="29" t="s">
-        <v>2053</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
-        <v>2054</v>
+        <v>2047</v>
       </c>
       <c r="B118" s="29" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A119" s="28" t="s">
-        <v>2056</v>
+        <v>2049</v>
       </c>
       <c r="B119" s="29" t="s">
-        <v>2057</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
-        <v>2058</v>
+        <v>2051</v>
       </c>
       <c r="B120" s="29" t="s">
-        <v>2059</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A121" s="28" t="s">
-        <v>2060</v>
+        <v>2053</v>
       </c>
       <c r="B121" s="29" t="s">
-        <v>2061</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
-        <v>2062</v>
+        <v>2055</v>
       </c>
       <c r="B122" s="29" t="s">
-        <v>2063</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="51" x14ac:dyDescent="0.25">
       <c r="A123" s="32" t="s">
-        <v>2064</v>
+        <v>2057</v>
       </c>
       <c r="B123" s="29" t="s">
-        <v>2065</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
-        <v>2066</v>
+        <v>2059</v>
       </c>
       <c r="B124" s="29" t="s">
-        <v>2067</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A125" s="28" t="s">
-        <v>2068</v>
+        <v>2061</v>
       </c>
       <c r="B125" s="29" t="s">
-        <v>2069</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
-        <v>2070</v>
+        <v>2063</v>
       </c>
       <c r="B126" s="29" t="s">
-        <v>2071</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="102" x14ac:dyDescent="0.25">
       <c r="A127" s="28" t="s">
-        <v>2072</v>
+        <v>2065</v>
       </c>
       <c r="B127" s="29" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
     </row>
   </sheetData>
